--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484112_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484112_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9721</v>
+        <v>4.5507</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3564</v>
+        <v>4.2997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6157</v>
+        <v>0.251</v>
       </c>
       <c r="G2" t="n">
         <v>4.3468</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7884</v>
+        <v>0.367</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1872</v>
+        <v>0.1305</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6012</v>
+        <v>0.2365</v>
       </c>
       <c r="V2" t="n">
         <v>-2.1469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2259</v>
+        <v>1.5647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.2222</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5389</v>
+        <v>1.3425</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0452</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7987</v>
+        <v>0.1374</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4933</v>
+        <v>0.0285</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3053</v>
+        <v>0.109</v>
       </c>
       <c r="V3" t="n">
         <v>2.0757</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4175</v>
+        <v>0.7236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6433</v>
+        <v>0.9494</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2259</v>
@@ -766,10 +766,10 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2097</v>
+        <v>0.0964</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U4" t="n">
         <v>0.0396</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3657</v>
+        <v>0.3005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6045</v>
+        <v>0.2587</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2387</v>
+        <v>0.0418</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2748</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4422</v>
+        <v>0.3769</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5613</v>
+        <v>0.2155</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1191</v>
+        <v>0.1615</v>
       </c>
       <c r="V5" t="n">
         <v>0.6032</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2067</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1886</v>
+        <v>-1.0016</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3954</v>
+        <v>1.0026</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1722</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4433</v>
+        <v>-0.649</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8161</v>
+        <v>-0.6291</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3728</v>
+        <v>-0.02</v>
       </c>
       <c r="V6" t="n">
         <v>2.6076</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2483</v>
+        <v>-0.4233</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8447</v>
+        <v>-1.2722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5965</v>
+        <v>0.849</v>
       </c>
       <c r="G7" t="n">
         <v>2.8138</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8122</v>
+        <v>0.0127</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1846</v>
+        <v>-0.6121</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3723</v>
+        <v>0.6248</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8692</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8492</v>
+        <v>-1.8047</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5435</v>
+        <v>-1.5831</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3057</v>
+        <v>-0.2216</v>
       </c>
       <c r="G8" t="n">
         <v>0.0558</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0788</v>
+        <v>0.1233</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1191</v>
+        <v>0.0794</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0403</v>
+        <v>0.0439</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5987</v>
+        <v>-2.1118</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.22</v>
+        <v>-1.7892</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3787</v>
+        <v>-0.3226</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5738</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0169</v>
+        <v>-0.53</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3004</v>
+        <v>0.1304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7165</v>
+        <v>-0.6604</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7851</v>
+        <v>-2.1922</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2539</v>
+        <v>-2.8855</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4688</v>
+        <v>0.6933</v>
       </c>
       <c r="G10" t="n">
         <v>-1.878</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.3855</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7481</v>
+        <v>-0.3797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2302</v>
+        <v>-0.0057</v>
       </c>
       <c r="V10" t="n">
         <v>0.0713</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.7767</v>
+        <v>-9.4315</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5442</v>
+        <v>-5.2552</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2325</v>
+        <v>-4.1764</v>
       </c>
       <c r="G11" t="n">
         <v>-5.8106</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.263</v>
+        <v>0.0822</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2436</v>
+        <v>0.0454</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0193</v>
+        <v>0.0368</v>
       </c>
       <c r="V11" t="n">
         <v>-5.0918</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0701</v>
+        <v>-8.823</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.303700000000001</v>
+        <v>-8.056800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7662</v>
+        <v>-0.7663000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-5.704499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>14.8787</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6153</v>
+        <v>-0.3685999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1813</v>
+        <v>-0.9345</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5658000000000001</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7501</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.949199999999999</v>
+        <v>7.5463</v>
       </c>
       <c r="E13" t="n">
-        <v>8.206099999999999</v>
+        <v>7.0837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7431</v>
+        <v>0.4626</v>
       </c>
       <c r="G13" t="n">
         <v>3.6952</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3296</v>
+        <v>0.9267</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4115</v>
+        <v>0.2892</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9181</v>
+        <v>0.6375</v>
       </c>
       <c r="V13" t="n">
         <v>0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5845</v>
+        <v>4.264</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8232</v>
+        <v>0.6192</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7613</v>
+        <v>3.6448</v>
       </c>
       <c r="G14" t="n">
         <v>2.2022</v>
@@ -1546,13 +1546,13 @@
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9142</v>
+        <v>0.5937</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3912</v>
+        <v>0.1871</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5231</v>
+        <v>0.4066</v>
       </c>
       <c r="V14" t="n">
         <v>0.6745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3333</v>
+        <v>3.0816</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8503</v>
+        <v>1.2381</v>
       </c>
       <c r="F15" t="n">
-        <v>1.483</v>
+        <v>1.8435</v>
       </c>
       <c r="G15" t="n">
         <v>1.8348</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9262</v>
+        <v>0.6745</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8787</v>
+        <v>0.2665</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0475</v>
+        <v>0.408</v>
       </c>
       <c r="V15" t="n">
         <v>3.5481</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3478</v>
+        <v>2.5596</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0387</v>
+        <v>0.3694</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3866</v>
+        <v>2.1902</v>
       </c>
       <c r="G16" t="n">
         <v>0.9994</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0403</v>
+        <v>0.1714</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6744</v>
+        <v>-0.2663</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6342</v>
+        <v>0.4378</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.451</v>
+        <v>1.8371</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8624</v>
+        <v>2.1684</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4113</v>
+        <v>-0.3314</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6925</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1224</v>
+        <v>0.2636</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4307</v>
+        <v>-0.1246</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3082</v>
+        <v>0.3881</v>
       </c>
       <c r="V17" t="n">
         <v>1.4724</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0494</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2102</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1608</v>
+        <v>1.3011</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2875</v>
@@ -1858,13 +1858,13 @@
         <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4166</v>
+        <v>-0.2763</v>
       </c>
       <c r="T18" t="n">
         <v>-0.238</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3373</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3323</v>
+        <v>-1.2678</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.4307</v>
+        <v>-3.6145</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0984</v>
+        <v>2.3467</v>
       </c>
       <c r="G19" t="n">
         <v>0.6598000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4807</v>
+        <v>0.5838</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4137</v>
+        <v>0.4025</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.067</v>
+        <v>0.1813</v>
       </c>
       <c r="V19" t="n">
         <v>0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2433</v>
+        <v>-2.6788</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.128</v>
+        <v>-2.9239</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1153</v>
+        <v>0.2451</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3448</v>
@@ -2014,13 +2014,13 @@
         <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.068</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4307</v>
+        <v>-0.2266</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2019</v>
+        <v>0.1586</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4724</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9708</v>
+        <v>-4.6826</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.168</v>
+        <v>-2.964</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8028</v>
+        <v>-1.7187</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3622</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8621</v>
+        <v>-0.5739</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0599</v>
+        <v>-0.8558</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1978</v>
+        <v>0.2819</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3417</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>10.07</v>
+        <v>10.7503</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7664</v>
+        <v>0.7662000000000018</v>
       </c>
       <c r="F22" t="n">
-        <v>9.303799999999999</v>
+        <v>9.9839</v>
       </c>
       <c r="G22" t="n">
         <v>5.704400000000001</v>
@@ -2170,13 +2170,13 @@
         <v>14.8787</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6153</v>
+        <v>2.2955</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5660000000000001</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1814</v>
+        <v>2.8615</v>
       </c>
       <c r="V22" t="n">
         <v>2.7501</v>
